--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>131900473</v>
       </c>
       <c r="B8" t="n">
-        <v>57165</v>
+        <v>57198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>131900473</v>
       </c>
       <c r="B8" t="n">
-        <v>57198</v>
+        <v>57211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>131900473</v>
       </c>
       <c r="B8" t="n">
-        <v>57211</v>
+        <v>57213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1378,11 +1378,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>131900473</v>
       </c>
       <c r="B8" t="n">
-        <v>57213</v>
+        <v>57223</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>131900473</v>
       </c>
       <c r="B8" t="n">
-        <v>57223</v>
+        <v>57224</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>131900473</v>
       </c>
       <c r="B8" t="n">
-        <v>57224</v>
+        <v>57227</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
